--- a/DOM/AFOLU/A1_Outputs/A-O_Fleet.xlsx
+++ b/DOM/AFOLU/A1_Outputs/A-O_Fleet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RD_Model_v7_FUNCIONAL\A1_Outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yds3\Desktop\RD_model_int_NZ6\A1_Outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76194D01-8B7D-4D69-9023-7CB05F676A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CA7823-CB54-4522-962A-751635EE2509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="138">
   <si>
     <t>Group.ID</t>
   </si>
@@ -444,6 +444,12 @@
   </si>
   <si>
     <t>Light Truck Hybrid Diesel</t>
+  </si>
+  <si>
+    <t>quedó en el SP de NTT</t>
+  </si>
+  <si>
+    <t>Ya se la paso</t>
   </si>
 </sst>
 </file>
@@ -693,9 +699,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -733,9 +739,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -768,9 +774,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -803,9 +826,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -980,7 +1020,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
@@ -1105,7 +1145,7 @@
         <v>2050</v>
       </c>
       <c r="I3" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>18</v>
@@ -1145,9 +1185,7 @@
       <c r="H4" s="9">
         <v>2050</v>
       </c>
-      <c r="I4" s="8">
-        <v>70.3</v>
-      </c>
+      <c r="I4" s="8"/>
       <c r="J4" s="9" t="s">
         <v>18</v>
       </c>
@@ -1187,7 +1225,7 @@
         <v>2050</v>
       </c>
       <c r="I5" s="8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>18</v>
@@ -1228,7 +1266,7 @@
         <v>2050</v>
       </c>
       <c r="I6" s="8">
-        <v>7.0000000000000001E-3</v>
+        <v>2</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>18</v>
@@ -1351,7 +1389,7 @@
         <v>2050</v>
       </c>
       <c r="I9" s="14">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="J9" s="15" t="s">
         <v>18</v>
@@ -1392,7 +1430,7 @@
         <v>2050</v>
       </c>
       <c r="I10" s="14">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="J10" s="15" t="s">
         <v>18</v>
@@ -1515,7 +1553,7 @@
         <v>2050</v>
       </c>
       <c r="I13" s="8">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>18</v>
@@ -1550,25 +1588,25 @@
         <v>2018</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
+      </c>
+      <c r="H14" s="9">
+        <v>2050</v>
+      </c>
+      <c r="I14" s="8">
+        <v>1</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -1638,7 +1676,7 @@
         <v>2050</v>
       </c>
       <c r="I16" s="14">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>18</v>
@@ -1679,7 +1717,7 @@
         <v>2050</v>
       </c>
       <c r="I17" s="14">
-        <v>64.599999999999994</v>
+        <v>29</v>
       </c>
       <c r="J17" s="15" t="s">
         <v>18</v>
@@ -1720,7 +1758,7 @@
         <v>2050</v>
       </c>
       <c r="I18" s="14">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="J18" s="15" t="s">
         <v>18</v>
@@ -1802,7 +1840,7 @@
         <v>2050</v>
       </c>
       <c r="I20" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J20" s="15" t="s">
         <v>18</v>
@@ -1811,7 +1849,7 @@
         <v>26</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="M20" s="17" t="s">
         <v>21</v>
@@ -1852,7 +1890,7 @@
         <v>19</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="M21" s="11" t="s">
         <v>21</v>
@@ -1884,7 +1922,7 @@
         <v>2050</v>
       </c>
       <c r="I22" s="8">
-        <v>2.66</v>
+        <v>40</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>18</v>
@@ -1925,7 +1963,7 @@
         <v>2050</v>
       </c>
       <c r="I23" s="8">
-        <v>4.9400000000000004</v>
+        <v>44</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>18</v>
@@ -1966,7 +2004,7 @@
         <v>2050</v>
       </c>
       <c r="I24" s="8">
-        <v>1.1399999999999999</v>
+        <v>13</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>18</v>
@@ -2001,25 +2039,25 @@
         <v>2018</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
+      </c>
+      <c r="H25" s="9">
+        <v>2051</v>
+      </c>
+      <c r="I25" s="8">
+        <v>1</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
@@ -2130,7 +2168,7 @@
         <v>2050</v>
       </c>
       <c r="I28" s="14">
-        <v>3.99</v>
+        <v>40</v>
       </c>
       <c r="J28" s="15" t="s">
         <v>18</v>
@@ -2171,7 +2209,7 @@
         <v>2050</v>
       </c>
       <c r="I29" s="14">
-        <v>7.41</v>
+        <v>44</v>
       </c>
       <c r="J29" s="15" t="s">
         <v>18</v>
@@ -2212,7 +2250,7 @@
         <v>2050</v>
       </c>
       <c r="I30" s="14">
-        <v>1.71</v>
+        <v>13</v>
       </c>
       <c r="J30" s="15" t="s">
         <v>18</v>
@@ -2376,7 +2414,7 @@
         <v>2050</v>
       </c>
       <c r="I34" s="8">
-        <v>30.4</v>
+        <v>40</v>
       </c>
       <c r="J34" s="9" t="s">
         <v>18</v>
@@ -2417,7 +2455,7 @@
         <v>2050</v>
       </c>
       <c r="I35" s="8">
-        <v>33.299999999999997</v>
+        <v>44</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>18</v>
@@ -2458,7 +2496,7 @@
         <v>2050</v>
       </c>
       <c r="I36" s="8">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="J36" s="9" t="s">
         <v>18</v>
@@ -2827,7 +2865,7 @@
         <v>2050</v>
       </c>
       <c r="I45" s="8">
-        <v>93.1</v>
+        <v>97</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>18</v>
@@ -2902,27 +2940,13 @@
       <c r="F47" s="8">
         <v>2018</v>
       </c>
-      <c r="G47" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H47" s="9">
-        <v>2050</v>
-      </c>
-      <c r="I47" s="8">
-        <v>1</v>
-      </c>
-      <c r="J47" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L47" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="M47" s="11" t="s">
-        <v>21</v>
-      </c>
+      <c r="G47" s="11"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="11"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
@@ -3114,7 +3138,7 @@
         <v>2050</v>
       </c>
       <c r="I52" s="14">
-        <v>55.1</v>
+        <v>78</v>
       </c>
       <c r="J52" s="15" t="s">
         <v>18</v>
@@ -3155,7 +3179,7 @@
         <v>2050</v>
       </c>
       <c r="I53" s="14">
-        <v>23.8</v>
+        <v>4</v>
       </c>
       <c r="J53" s="15" t="s">
         <v>18</v>
@@ -3196,7 +3220,7 @@
         <v>2050</v>
       </c>
       <c r="I54" s="14">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="J54" s="15" t="s">
         <v>18</v>
@@ -3340,10 +3364,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CCDA0DC61E44874FB77B81A0A8C300E4" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="71904d85c9bd1373b9e56b88e8365113">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c2c21c4-f980-47d5-be5b-1bb924ee96a2" xmlns:ns3="1b6bb729-2ef5-410d-b4d4-7ced22c361d1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7f50eb003d4f8624802c7eda0096d7ec" ns2:_="" ns3:_="">
-    <xsd:import namespace="9c2c21c4-f980-47d5-be5b-1bb924ee96a2"/>
-    <xsd:import namespace="1b6bb729-2ef5-410d-b4d4-7ced22c361d1"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000D404091916B8749A73FDE0336A1D2B1" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="97d759966af21adcadc0b99feda85e1a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="160a8fee-1065-46af-a09f-4bc299cd7729" xmlns:ns3="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c4a9b885529ac7a0313cb8fba8dc54f0" ns2:_="" ns3:_="">
+    <xsd:import namespace="160a8fee-1065-46af-a09f-4bc299cd7729"/>
+    <xsd:import namespace="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -3352,18 +3376,13 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3371,7 +3390,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c2c21c4-f980-47d5-be5b-1bb924ee96a2" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="160a8fee-1065-46af-a09f-4bc299cd7729" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -3384,91 +3403,52 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:displayName="Etiquetas de imagen_0" ma:hidden="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="21" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1b6bb729-2ef5-410d-b4d4-7ced22c361d1" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="14" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="TaxCatchAll" ma:index="12" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{358d400d-8031-419e-a2bc-623ab747dbff}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99">
       <xsd:complexType>
         <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
+          <xsd:extension base="dms:MultiChoiceLookup">
             <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
             </xsd:sequence>
           </xsd:extension>
         </xsd:complexContent>
       </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="15" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -3480,8 +3460,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -3571,16 +3551,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9c2c21c4-f980-47d5-be5b-1bb924ee96a2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3589,24 +3559,34 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="160a8fee-1065-46af-a09f-4bc299cd7729" xsi:nil="true"/>
+    <TaxCatchAll xmlns="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D2EB738-4B03-4875-9A4B-0875FA875E44}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DF14314-21A0-4D45-A449-E19FA677B848}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2942FC4A-C68A-4BDC-8EAE-FEB2B1D88B55}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36CF4A2E-7F59-4801-9032-73CA83CC34AA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="c4f98862-adfd-4d9c-a945-852f80f0eb51"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2942FC4A-C68A-4BDC-8EAE-FEB2B1D88B55}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="9c2c21c4-f980-47d5-be5b-1bb924ee96a2"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>